--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vacantes Activas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vacantes Activas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,57 +430,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Secretaría de Educación</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Área de Conocimiento</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Tipo de Priorización</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Postulados Actuales</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Fecha de Cierre</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Enlace Sistema Maestro</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
         </is>
@@ -535,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -590,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -645,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -700,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -755,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -810,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -865,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -920,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1030,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1085,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1140,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1195,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1250,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1305,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1360,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1415,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1470,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1525,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1580,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,88 +413,461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Secretaría de Educación</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Área de Conocimiento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Área de Conocimiento</t>
+          <t>Tipo de Priorización</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Priorización</t>
+          <t>Postulados Actuales</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Postulados Actuales</t>
+          <t>Fecha de Cierre</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de Cierre</t>
+          <t>Enlace Sistema Maestro</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Primera Detección</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace Sistema Maestro</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>03/09/2026 09:22</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>eacd70a327679cdc882c7554e2f57848b73b51caba083993ad7b7abe4350b065</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>03/09/2026 09:22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6d403e7bafc7ea80b3f083a8c3b40e27579ec379850863a31e1f89063292b502</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>03/09/2026 09:55</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2b751c1bc3f1a1c5ab1a04464f5ae5663e3e95075e82111afb584a58097d9f68</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>03/09/2026 09:55</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3bcf8002845b1200b68d6f72af777e1f745bf19318c8f03a3e0a387d20e6e765</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>03/09/2026 09:58</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>f5cf93a0aaf66845c9a9e6a28cbb75fea0e466ff8dad54999dad7fd00b71a032</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>03/09/2026 09:58</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>a07b39e8fc35c05df123b5c7825461a196ca997a37861b4d757a4e96c7a1aab9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>03/09/2026 09:58</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>26127de19e702f5e9856ebb83e71e752308d66d946d2e0a275880e8d31d58183</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,15 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -868,6 +868,1271 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>26127de19e702f5e9856ebb83e71e752308d66d946d2e0a275880e8d31d58183</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>88</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:05</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7fade7c20d3bc5b4248db4b20268dcc694fc14c59b47c5e192dc63c39e390883</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>23</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:05</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7a79d4d4674be6b0feb339e2d7ae38f50be7f6604e176feb46c1d534d81c7bf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Algeciras</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cuatro</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:17</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>70fdcafed900d107ab61c625087b573034bcd8db443b37e96c34df79fb505472</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>San Agustin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>45</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:17</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fd63dc836c7ee73c5ecc0721026813591fb5e34db2818a13d5c00b3d3da8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Garzon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cinco</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>34</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>9394ca799fb186c24ad1edef2f7d650eac58b2c5394ef67ee515ab47fdd48edb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>21</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:18</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>b695469e192267a3ab60fcbf5b524313a5322944ab9fe712570127708e4d8b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cabuyaro</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>27</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>9c5422ed913266135089fc11e0374f75e72a3fbc3b308bef57f45313066ebe23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>La Macarena</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Zona 8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>19</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>d471c031a6377d40ee62904f67e1fd18d1e6a4abf9066a4b12605f81573d08c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>La Macarena</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Zona 8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>22</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>408e03375d83c2ed8286596c2960fb0d7209777522bb6581d32a57bcf896c8f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>La Macarena</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Zona 8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>d029448c801510367028b2af56eb90ff1230a420079c4f8c53a7bb839c4cb48c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>La Macarena</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Zona 8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ca1e38ed9532644e082abaa1254a134d75febfcbac606ab5a7bd72a5fdc57b65</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>La Macarena</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Zona 8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>23</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7bab37a13efe21c1e4ea099648c38d19a2ab44b8b39b6bab08251d04785e445f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lejanias</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Zona 1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>28</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2f47fb0d0545b5adba3162ed5f7baca713608622c60a35ea1698f886555f1953</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mapiripan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Zona 4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>21</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>3360d614976ca7cf03ac15bdda15ca8bbf2209570c8548a6f2edde57125cf26c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Puerto Gaitan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>01cb57b58c7dd458169ee05bca6db5e806784c31b0c4bd976fcb95f573d7bc63</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Puerto Lopez</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fc2fd807b6bb881f0bff295f5769f7ae513d973062dafc85fb25addd629c339e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>San Carlos De Guaroa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>7</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7c4dfdeceb0599f9b4214636a92dea48bd35a71d46effe0a773adfaa8578c6ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Puerto Gaitan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>37543b197ef77be6a14183dfd274ba63d92e35eb3863f6f97537d221d162f448</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tulua</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>21</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>868113275c5e645458820e61f6dd107f80be8101b7175b63ba525ab859ec4f19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tulua</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>42</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7d392eb7b4a40baf323056876eb9e28eaae2b1e5b5b13d547b3ad88803aedd73</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:26</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>63092222ab3695e5abc94a7a8dc43d723ea3bc482203aac64896b89c06ba92c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>35</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:26</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>c1ba4c748533380c212576f8bfc5e15a22c19b8cff1f516657858b7d57a9ed86</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>8</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>03/09/2026 10:26</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>233b49936b3257cc7fe2be36f710a3f0a98e1f441455367f8d00a0b515ed888b</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,88 +413,241 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Secretaría de Educación</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Área de Conocimiento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Área de Conocimiento</t>
+          <t>Tipo de Priorización</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Priorización</t>
+          <t>Postulados Actuales</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Postulados Actuales</t>
+          <t>Fecha de Cierre</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de Cierre</t>
+          <t>Enlace Sistema Maestro</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Primera Detección</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace Sistema Maestro</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>San Jose Del Guaviare</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Jose del Guaviare</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>04/09/2026 11:34</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>773d9367106e68d2f3219f536fc2937acca50042630d9fb12b36cbf8d923fd84</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>San Jose Del Guaviare</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>San Jose del Guaviare</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Docente aula</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>04/09/2026 11:34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>037ff3472a033f594ba851d543d82af16b76e03d8f4ce3f905771ce3799ac3bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Docente aula</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>04/09/2026 11:34</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>21fefd647fa961833c785b538f597783d3b4511b2e5310eb3a6f90ef9884174f</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,241 +413,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Secretaría de Educación</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Área de Conocimiento</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tipo de Priorización</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Postulados Actuales</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fecha de Cierre</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Primera Detección</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Enlace Sistema Maestro</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>San Jose Del Guaviare</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Jose del Guaviare</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Humanidades y lengua castellana</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>61</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>04/09/2026 11:34</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>773d9367106e68d2f3219f536fc2937acca50042630d9fb12b36cbf8d923fd84</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>San Jose Del Guaviare</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>San Jose del Guaviare</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Docente aula</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Matemáticas</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>38</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>04/09/2026 11:34</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>037ff3472a033f594ba851d543d82af16b76e03d8f4ce3f905771ce3799ac3bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Miraflores</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Miraflores</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Docente aula</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Matemáticas</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>37</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>04/09/2026 11:34</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>21fefd647fa961833c785b538f597783d3b4511b2e5310eb3a6f90ef9884174f</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,88 +413,1066 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Secretaría de Educación</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Área de Conocimiento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Área de Conocimiento</t>
+          <t>Tipo de Priorización</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Priorización</t>
+          <t>Postulados Actuales</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Postulados Actuales</t>
+          <t>Fecha de Cierre</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de Cierre</t>
+          <t>Enlace Sistema Maestro</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Primera Detección</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace Sistema Maestro</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>05/09/2026 08:59</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dc73f6344a8dee2944ec5fc9960dc2af130d473ecd073575fe7221179ca39ea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>05/09/2026 08:59</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>60207b1a0b64c148bd08e42f1f21935004190474bfe52e3bbf6b33bf98805eb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>05/09/2026 08:59</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3b6b1a9c49bb9c03e9dcbcfdead48e1bec7788681850a9e127d4b816f7cf929c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>05/09/2026 08:59</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0c723fa49ffb131c914a77bba4e8e4a1e2d1cb3077cc5cb0d72ca8ec69d9c7f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>05/09/2026 08:59</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>f17f2b8ebd59158b5226a9ce015965c52c4d6c7f54562ad521c296a04b36323f</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>05/09/2026 08:59</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>df1006847aff851fad2c017ad2dc41d4d3632ed50e5138b3c98b03fbef28a6d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>El Rosal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sabana Occidente</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>bc8fac20e1c620101c33f0a820948edbdf45ab0882c3564f548e357225a970bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Caqueza</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>261f1597f1eac4acd8a9bd8cc1b439a03fd3184ea6042608dce51a7c6196480b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ubala</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ubalá</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>522cb6279b98d39391668f8d545c97f12b3f3403c0ca20a54fd8e42fc1697805</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Guataqui</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Alto Magdalena</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>15de09e19fe473ea5ceb5aad879a23642d1387a7adbe2c9f83aedce78663689d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quebradanegra</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gualiva</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:13</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>08e7be50f00612720a501e5539e5f79eb0eb6a7e38e1a09beb57bf52317674cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Villeta</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gualiva</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Idioma extranjero francés</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>66ef0f939937c68f2b3b6b723bd629df9730d47e6ae1778be9ade17c1a479ac1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cogua</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sabana Centro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ciencias económicas y políticas</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>c1f31c2b453b047971a01e5aed7727407e5d1c618d1a0016a7cdd5b83e87208c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>San Antonio Del Tequendama</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tequendama</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>a1334a88573a2126ad7eb2f5192c3bb3648fe2b921e88e941c01e1ce02495e8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rio Negro</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>f5fd759dd5dec6900aa74923407654ba5ece58ebd4db11a9b7cc11d0386be8cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0b204586d140586f03c8e26f3cf244a92948f6212a0e5a38d977705f021cd89b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:51</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>c8bf79b545ed8e40b6dca1adb67973ed97b5ff6647b01f3f442f0772eca2a0cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:52</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>de10f196c8ccac3480e4f5e62dd1f00848f7ebebc613abe918c84e7bad0a1e6f</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1473,6 +1473,501 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>de10f196c8ccac3480e4f5e62dd1f00848f7ebebc613abe918c84e7bad0a1e6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>23</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>05/09/2026 09:58</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>a0733c70925daa6a9b85945348ef78303efb1a742bbb54557fcb016e2542fdd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Topaga</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sugamuxi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>29</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>613356070592629c823ca346c109000fb4da53c64dc36e37e253e6d32bb90020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>35</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>d86bcb0e884e8cca84f6bad53f45fab422acbc924800755f29a1eeca9c11c24a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Maripí</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>18</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>d3c1a6f7cc69468236416b6d733461c4b36405af401db121d631a14affc71913</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pauna</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>27</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>c6efd23b4414cfc81be703032c710f466c0ec0533a3051290bbc60e87a46161e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>El Cocuy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gutierrez</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>48</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>76fd5e1d0fa50f322af7502287d1d119ffc470af80d5c09e09c9d82e00b84261</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Labranzagrande</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>21</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1ead80235842f9643e63635b097959838692077ca8a628f6d2035387cf664339</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>San Pablo De Borbur</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>32</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5d6cb4343ae5a95e30f039a25210f4745d547e98594dd004172ce3ca68d74ad3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pisba</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pisba</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>22</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>05/09/2026 10:04</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>66407e6314a674c12acb3ee10f38c2adcf145b0614a0c0c1c55238e65781c4bb</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,88 +413,131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Secretaría de Educación</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Área de Conocimiento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Área de Conocimiento</t>
+          <t>Tipo de Priorización</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Priorización</t>
+          <t>Postulados Actuales</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Postulados Actuales</t>
+          <t>Fecha de Cierre</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de Cierre</t>
+          <t>Enlace Sistema Maestro</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Primera Detección</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace Sistema Maestro</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>San Gil</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Guaneta</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>09/09/2026 11:59</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ece824eabc13fbb3fa2da3a8aa70bf187553d0a8d98901862f65d2dadc0e0445</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,131 +413,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Secretaría de Educación</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Área de Conocimiento</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tipo de Priorización</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Postulados Actuales</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fecha de Cierre</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Primera Detección</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Enlace Sistema Maestro</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>San Gil</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Guaneta</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tecnología e informática</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>77</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>09/09/2026 11:59</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ece824eabc13fbb3fa2da3a8aa70bf187553d0a8d98901862f65d2dadc0e0445</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,88 +413,1341 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Secretaría de Educación</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Área de Conocimiento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Área de Conocimiento</t>
+          <t>Tipo de Priorización</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Priorización</t>
+          <t>Postulados Actuales</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Postulados Actuales</t>
+          <t>Fecha de Cierre</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de Cierre</t>
+          <t>Enlace Sistema Maestro</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Primera Detección</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace Sistema Maestro</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:14</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>cd63bd77bacf52958b98b34cef2d330c19d7f3f54fcfd40774d13c53aa720fb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>51812ee0ab2eabd51bcdd6fbe8d7052ce484997bdb5c005cdb375bfeb475fa8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0c6425a302d4788a8d7fedb753828be1e49cbb0455e5bd56da8d13d1d59c8c05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1c73b988f6e7ca34d97ec7643f31205988ef6cdea3cb4eca642678d48d932ee7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>21dad92aa9ffb694a814f136af101c5ed758d0844397d80e51aa387f1359c421</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>c00237b3effe6c68d543437b56186d2b787de694b0778f11b5842e1761851a21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>aa79d544b8bc5537c762255b2cb4ce95240a218e6ba1c89693f0a0de6b34c8b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>978d143c6fb706ec23785790a5c0327b10d01fcb0a93e249d167e467985641a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>feb64407668cf7d199bebac2a2f4571da65d086bec5a76ccd9bf4a04339db7e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2538aec3668d89562dc9b0d638f67717dc0a0585e35da490f4cbc0b893e0638d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025b84b437feb6fac8ccbf85f2904b095a8ff9eaf09f345aa467601ab745119</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>11</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>209b8556a311d1d959847d01e4a4fdf17a3f419a1487ed406c007e1bbac15b4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1a2113ea1a5e505d36c854d3d024411d8f7df830e2ef71f560b4c9585d1b55cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vigia Del Fuerte</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Vigia del Fuerte</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>eb94b6215a2428b3525d0b718e91b13568a834a5c2941701b4fae08d856acea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5c75a348d19d1a77f21ce55990038ca40abcf4f1bd87ab02699b848e1689ce4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>f7fcb016da2504cc20b895add94bf5ec9067b210134dfb9a6357777e031deb2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ebfa25c341d1a1d6a5c9a22de2d710cf94d5d7edbb77a6ef8640e0153cffcdf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:17</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ce4a48a8f1cb1c1fd24bd3b6c1cdeab3fb4da980354a5380d064b1b642a2cd9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>El Santuario</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>23</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:18</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>d52a4dea7ae0b201e9a0a2e85271bd357649c016766b8c4cecca1746643f3429</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>63456ad9baf8d2d6b3890208b409add5192bde3bd8897c8d84a3bdc08925008d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:23</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>917482b2c710a8cb40b25dc468f984840f2d8c3b373343a46e83a75990287fa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:35</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>43c528becdc1e48e806d4e71ab6aa257b40e40df506bd0d83fcb52c20040647a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:43</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>362c9fecd172a44aef723157ea39f92a2444fe981deb5be38565be89c1be9ec1</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,21 +1733,2221 @@
         </is>
       </c>
       <c r="H24" t="n">
+        <v>54</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:43</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>362c9fecd172a44aef723157ea39f92a2444fe981deb5be38565be89c1be9ec1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>81</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:43</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2c013b498527e93e72caf03854bcda5547ba2bc7c3611b51e54e477c6e9ec030</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>70</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>cd4f5018a5fce99012860b9be0cb6153773616a932e2fe66402f16b7d8c4c020</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>cc6ca396450b64fa776408e4266b71f200caf85933d8b881b395353ea13d9ef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>San Cristobal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ecaad212f542c2c0057e2c8085acd5cd091958e14a4c71f116325bf1d9c26a30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tunjuelito</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>13</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>b0f71aa28153856c395c7d3ab1f2f6137b58a5ba4af2ccb2fb60f79ff0eb792f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>53</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>a7f7c4b37e4fcb2fdfb5a197fd5d92290793f7d5ebd3d77442da34fb6ed57e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>29</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>4a7f9f41e8609a103a91dfd5ba0c74850f971895ebe4362d591d956bb63b3b7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Engativa</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>b1bae89eaf20cc8089752b01c3158e4af8b8c5bd3ef7c1b635d34b5abbcd79b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Engativa</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DOCENTE ORIENTADOR</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>71</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>3994bd149c200d9036ef9d4f17cbd616a4618704b086d1941b6b4e13e41c0dbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Suba</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>17</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>d38a53ace61e7b451d8d71f7903a2516c59851e5cc623afee280bb74a4ca350e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Puente Aranda</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>58</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>38db577605429baa2b0d2f79f1ff655605e6086d678af02ca8b86c886c5a60ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Puente Aranda</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>32</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:45</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2f8728745210c4eba7292dca56dff5a716048ad5de1c30cadf905c700f1f53fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Rafael Uribe Uribe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:45</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>920f579697c1275f4f68a9cbfebd9f0f0a8510e4e469dc1cd0a220cf41211afa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Rafael Uribe Uribe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>9</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:45</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ce748d08be633f6a8915ce56fa01bad942489f01860d2b3b630c17cdc05a609a</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Acevedo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>58</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:49</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>76fe6459cb9ecc125ff0c48010e9ec8111da1df45f738f258282d5589debccc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cuatro</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>90</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:49</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>56f1d284d754a6a96c114162be6fe413e857f3b2990bdb8364b2ffaaaad773e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Campoalegre</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cuatro</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:49</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>971e8575a3afd074a07c0dbf189028a37878a5b443768230a6df7ae1bf83dcfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tello</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Dos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>20</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>9a25e6800e54dfc94282872302253259734c16cea2904b6490c4300dbfeb0f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>62</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:59</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>61eccce58a388d0ea3c6c333e2dd648db746c68a4a88a2c9eefe21964af7507f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>25</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:59</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8d0320094e93e56211fdc094e884db7ca823066c35264d2b5a048d9336dd9b79</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>32</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10/09/2026 09:59</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>53889bc837266d147bdb8c0d0b570532616b5e6b82b406e7d3034ea09074f41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>54</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:02</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>f26524771a50749744c9e209a7250ecb3a83b1e32fc087e2b59d6895c8993255</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
         <v>21</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10/09/2026 09:43</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>362c9fecd172a44aef723157ea39f92a2444fe981deb5be38565be89c1be9ec1</t>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:05</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>466f550838cb1c1eca44db7300b632672b94be62ce7571c43e4e3e48f54c05f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>9</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:11</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>5d0e7362ab41238cc88e20752e80a9dabe1834da07b6a4e3b5c653cc3653d2c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>25</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:11</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ba636bb78e6e70886d32230fdebcaaa396bbf837d976e4368c31430fee09c523</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>47</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:17</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>57ac4d0072b691872354ac08c154450bb85a74e3e9be2330502f759e73db5a9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>41</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:17</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>3932210f51ed8584f54633c03e040e79cdc11d5a3fec412e3e44efd3ec7920cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>28</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>41471b009ec56bea4105263d57181632d22a3043821e112d9cb7ed376ff90d99</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>San Zenon</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>San Zenon</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>448ce5f34bfe55c8b84884b62737e68c8ef08da31ad2e061ceb40b4d4437c1fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>a0a3bd0510157cf5da6d325b78de6432cc682793ae42d718f7a21410c1d48416</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sitionuevo</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sitionuevo</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:21</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>28e5b3cb2a3ed870a66bc75c571db5840b2b5e97b509529d2d92b1eb762e2a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>14</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:21</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>6a02efced17d1dbd3d57bde3b1ba50136d32b31a87a0bafa2a843bcc878d9ef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:21</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>409dda958a673b06c4d449c2855bd3ef805036361a7251c14311a98cd32c688c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Zapayan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Zapayan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:21</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>e173a387903f91ce001806ff4fa396ca251d96c785799c2fe8f7c20abb84ee3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Zona Bananera</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Zona Bananera</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:21</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>40069b6292f6cd92eda89451f896214843ad4e0b14a9df96c0ace2d6c7533971</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Puebloviejo</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Puebloviejo</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>6</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:21</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>e016725162c73bf73a9cdbc57efb2880c112c9a5a761523385586d2b0e6fab70</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Arauquita</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Arauquita</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>17</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:43</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>982daf24a64bef332342e2f498ca0d4600b57b9ff3504dc72d41111d07cac3b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>24</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:43</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>defc3fc2447be3f69505e7aad606d1cef060c75784e627f7c300d493cffad2b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>46</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:43</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>71b0f9b878fed59da602db9125bda7a6c4aa1794d6045fbe3fa04af5b7714dbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>El Tambo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>El Tambo</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>29</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10/09/2026 10:45</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0fa2395595a3fe89f76658a01b5ee569f461aa3d2fde819e1488858404ec245d</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,88 +413,131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Secretaría de Educación</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Área de Conocimiento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Área de Conocimiento</t>
+          <t>Tipo de Priorización</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Priorización</t>
+          <t>Postulados Actuales</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Postulados Actuales</t>
+          <t>Fecha de Cierre</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de Cierre</t>
+          <t>Enlace Sistema Maestro</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Primera Detección</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace Sistema Maestro</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Leguizamo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11/09/2026 11:31</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1a6e9add6390b282950364db8f079b29b139ff098645d314c6f2a4f5492c0a22</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
@@ -523,21 +523,241 @@
         </is>
       </c>
       <c r="H2" t="n">
+        <v>51</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11/09/2026 11:31</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1a6e9add6390b282950364db8f079b29b139ff098645d314c6f2a4f5492c0a22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Facatativa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Facatativá</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Facatativá</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11/09/2026 14:29</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>e202048c9b311a8a563f2a583254e72141ac28f6f01fa3d928fe613b761e0a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11/09/2026 14:30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8780c3d364d8d7622cce05d54a1999f8ac394794c92af831cc756b9ef614a598</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11/09/2026 14:30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7188722bc7bc876dd69d1a88176ae4c77ba68f5bbdb3dc2c6b7d05a7095a2b24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>7</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11/09/2026 11:31</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11/09/2026 14:30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1a6e9add6390b282950364db8f079b29b139ff098645d314c6f2a4f5492c0a22</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>db7d707d12645adf9d1bb77e8889d1395c0dd631983e9dceaa125b6865808186</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,15 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,21 +743,2331 @@
         </is>
       </c>
       <c r="H6" t="n">
+        <v>37</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11/09/2026 14:30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>db7d707d12645adf9d1bb77e8889d1395c0dd631983e9dceaa125b6865808186</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Altos Del Rosario</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Altos del Rosario</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7a33ef646041984df2257d300f462d0d4492765797422f58d178e4dfa2989f26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cantagallo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cantagallo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7a68336a584f817ec39a2347e8c649dfa6bfb06d38eb79a8fe0604568d077dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>San Martin De Loba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>San Martín de Loba</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>369f8a3edd4897f3a96dcdfd0be7f92d0fe7a4ab3fa9f22a5c86a569b8580fd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Santa Rosa Del Sur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Santa Rosa del Sur</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1765534a9ed762834be9633e70dcbfa8b9907c0434c7c1a38aaa3b7d900b16b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Talaigua Nuevo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Talaiga Nuevo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>a8226df3886a79c3548a3798597072de31bb01fb179052e1d86ece78a2100aa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>f94f903004b7039ecfbfbde8a673374dae5cf1645c5573fc6faad88574cdbef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>f607536e570b4fccc4d525d4e2b40713fa9374e2414e47f90c29d7a44bd6be99</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cantagallo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cantagallo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12d4ab9fd5a702118875367603edd256158a93908f86ea68f63e841e78c891ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zambrano</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zambrano</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>7</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11/09/2026 14:30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>db7d707d12645adf9d1bb77e8889d1395c0dd631983e9dceaa125b6865808186</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:51</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>b0d8287f0ed348b88eeee02f6449fb59b43b8d437d8ca564f7025933b7db41b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:01</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8c467fb81e0ad8e625741781c0e0023e6390ac3d4a5703fed8a98209e9bf6918</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>881f51aa2483611b7072493a9957de43926bd778316aa9ff891e8bb92ccdcbe9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>29</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:02</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>a9ef72bf4d7e6b6888c6060371527e30cd61f7905a2786a6d67bdef4d5662965</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>cbfba16edb967850b043f69266f64248e64ddbcfd7320bc03de2e543a80b2a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>720cc562701580da6b506f403be0e724569d5acc75e68e04f7404ae1a675dc92</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>b4de47f781cba158a190a1817e3fe9d0b97af2666a48e70ba879bd00d1a4f79a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>d9f0b9780654d78dd46a1b2d24e9c011f8c1cbb450bc84dd14e9a250cf1c3c35</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ebefbb83979e1be543aa793e8cd1b622583fd0bd2fd7a4432d8ebb886e842cbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>a3b426d18331cef712da0ab176e84b08b01ac925ab4a0aa0e10dc6c9cff088a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>81cd1171f65ceb62496ffb5ebf58cf2dfe22904f927bc645c75ea9e4237e4137</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2484ff6e09f2ea4386f766487692264916c7605c6bbd57eb092ade8fd0f9aaa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Curillo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Curillo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>da58c17a89c2b363d2471f6f29c0883b4e49f8ae39a6d131733c5edab50e1bda</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>La Montañita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>La Montañita</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1529df47813e2dc5869d7bacf0594896ce246f25992ffe2c5c07b247245d6d9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>a0fbe9de5d503afa2e59cab0c87a8b417c35942d6b8bc452fac7caf2b422720a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>San Vicente Del Caguan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>San Vicente del Caguán</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:04</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>c806062091c0fa36e28850dd68ce68cf2c0b7fd48093fe8b4a563b472131fe0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>San Vicente Del Caguan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>San Vicente del Caguán</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:05</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>3e826697bb5349ea72ea02ea3c132e9e5f347bbb239dcb349de52de02dda9abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>San Vicente Del Caguan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>San Vicente del Caguán</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:05</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>38abdbc562d6952bb708be6afae338bad07593a3cf5e71b54ee3fe03eed77f19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>San Vicente Del Caguan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>San Vicente del Caguán</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:05</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>39922026d37b6fd9df50be20563e802e9dfb3bb29895839a1b3dc46398cddeba</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>9</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:05</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>cbe152b8ffec22c41f92795cffffe5aa24c259382e978f4082953dd1ef0cbabb</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:05</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>72ebc399dee934ed2b27c1e608ceb3c9c37e5901ea86f58b09a2641366967c0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Solita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Solita</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:05</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>c669d93bcb1f6e3dc822dfff27c70683ca40a17ab59e05a6002e40ed22357551</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:05</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>968a6ea5a611c4434572825fd1a2bbf3c534f6959267040f2126c6970b86b149</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cachira</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>94f22bda2def659788843da0815ca4fef045dd82fd34d732500e5004f06d958d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Catatumbo 7</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>dc60b0f33ad437c34778939d4f1253bc231c09852d0cf126bbffed084242237f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>El Tarra</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Catatumbo 1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1a727bdc8e229cdb4751957c1df7e2112c3cdef53f612ed9d219043125a313f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Catatumbo 9</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>d555a67bb7ec272dd23796969fa94a562b98a5863d3fdd0b5c50d54ce51ab582</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>San Calixto</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Catatumbo 5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>af06c0bbfab9228267e683356d9752935204e87711b6e58dd758038c1a3ef133</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sardinata</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Catatumbo 11</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:07</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>209e9f0d32b631a1bad0ce79cdcc2c41d8dda9784c575fafd896f592ecc4d576</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Teorama</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Catatumbo 8</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:07</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0a2f612fa7ba72c6da56f481b0bc9f7b98094f7588881adb56da34b60eae3fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:07</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1a36bec9a64fdd63929756b7698367815f3b33baeababd9d71e870786c3c0f28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:07</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6271f194f1dcb5bcda2077fd6f0a65e22aaf147c36249f8b38cc8781c6b7999a</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:07</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>00c9ba000d2e78eb3020f893145906b9f87c7c14a57cde7f05f47dfa22efba76</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Villa Caro</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>11/09/2026 16:07</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2a3ae2a386358ac7998864a4431b6ac2cbf1b4a5c6c6274d401828d595c6ad31</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,88 +413,131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Secretaría de Educación</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Área de Conocimiento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Área de Conocimiento</t>
+          <t>Tipo de Priorización</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Priorización</t>
+          <t>Postulados Actuales</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Postulados Actuales</t>
+          <t>Fecha de Cierre</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de Cierre</t>
+          <t>Enlace Sistema Maestro</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Primera Detección</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace Sistema Maestro</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12/09/2026 16:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>c69f031e671c2ec29a4ae43325a50d7cb817862ef23699bf3a9a25c44e7e913c</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>

--- a/data/exportaciones/vacantes_actuales.xlsx
+++ b/data/exportaciones/vacantes_actuales.xlsx
@@ -413,131 +413,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Secretaría de Educación</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Área de Conocimiento</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tipo de Priorización</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Postulados Actuales</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fecha de Cierre</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Primera Detección</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Enlace Sistema Maestro</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Medellín</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Medellín</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Medellín</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Matemáticas</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>102</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12/09/2026 16:00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>c69f031e671c2ec29a4ae43325a50d7cb817862ef23699bf3a9a25c44e7e913c</t>
         </is>
       </c>
     </row>
